--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.36158576509662</v>
+        <v>12.2462576868282</v>
       </c>
       <c r="D2" t="n">
-        <v>21.21320343559643</v>
+        <v>3.447145558284419</v>
       </c>
       <c r="E2" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F2" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.0120622358531</v>
+        <v>9.58946011332613</v>
       </c>
       <c r="D3" t="n">
-        <v>4.582321200822502</v>
+        <v>0.7446271951336566</v>
       </c>
       <c r="E3" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F3" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.84930753964748</v>
+        <v>10.37551247519272</v>
       </c>
       <c r="D4" t="n">
-        <v>16.90578420237228</v>
+        <v>2.747189932885497</v>
       </c>
       <c r="E4" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F4" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.12930840313131</v>
+        <v>9.608512615508838</v>
       </c>
       <c r="D5" t="n">
-        <v>25.83118270617898</v>
+        <v>4.197567189754084</v>
       </c>
       <c r="E5" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F5" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.87226265548851</v>
+        <v>3.229242681516883</v>
       </c>
       <c r="D6" t="n">
-        <v>19.46028067992103</v>
+        <v>3.162295610487168</v>
       </c>
       <c r="E6" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F6" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>76.4484943724238</v>
+        <v>12.42288033551887</v>
       </c>
       <c r="D7" t="n">
-        <v>46.38274392746036</v>
+        <v>7.537195888212309</v>
       </c>
       <c r="E7" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F7" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.46491132142055</v>
+        <v>6.73804808973084</v>
       </c>
       <c r="D8" t="n">
-        <v>41.90556442691506</v>
+        <v>6.809654219373697</v>
       </c>
       <c r="E8" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F8" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.87386442355287</v>
+        <v>8.104502968827342</v>
       </c>
       <c r="D9" t="n">
-        <v>50.31063676394058</v>
+        <v>8.175478474140345</v>
       </c>
       <c r="E9" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F9" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.97428593950227</v>
+        <v>6.658321465169118</v>
       </c>
       <c r="D10" t="n">
-        <v>41.24843095492964</v>
+        <v>6.702870030176067</v>
       </c>
       <c r="E10" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F10" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.8587325409497</v>
+        <v>5.339544037904326</v>
       </c>
       <c r="D11" t="n">
-        <v>39.77905508653836</v>
+        <v>6.464096451562483</v>
       </c>
       <c r="E11" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F11" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.382581091071712</v>
+        <v>1.362169427299153</v>
       </c>
       <c r="D12" t="n">
-        <v>25.67968925973895</v>
+        <v>4.17294950470758</v>
       </c>
       <c r="E12" t="n">
-        <v>20.75789749288361</v>
+        <v>3.373158342593588</v>
       </c>
       <c r="F12" t="n">
-        <v>13.76979894529752</v>
+        <v>2.237592328610847</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
